--- a/api/templates/geneXpert_M4B3_biological_products/vi.xlsx
+++ b/api/templates/geneXpert_M4B3_biological_products/vi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\ahernandez\repos\aspect\api\templates\geneXpert_M4B3_biological_products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02012097-CB5F-4E45-9DB1-F193D02C6643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2D4E82-8588-4381-8299-4BD612AF7428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24D7A4EE-8982-41AB-893B-67BF3AF2DD3B}"/>
   </bookViews>
@@ -777,6 +777,22 @@
       <alignment horizontal="left" indent="4"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -793,28 +809,12 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2095,26 +2095,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
       <c r="F1" s="1"/>
       <c r="P1" s="40" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
       <c r="F2" s="1"/>
       <c r="G2" s="3"/>
     </row>
@@ -2126,45 +2126,45 @@
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
       <c r="Q5" s="6"/>
     </row>
     <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2172,26 +2172,26 @@
         <v>27</v>
       </c>
       <c r="B6" s="18"/>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
       <c r="G6" s="7"/>
       <c r="H6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="54" t="s">
+      <c r="I6" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
       <c r="Q6" s="8"/>
     </row>
     <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2199,30 +2199,30 @@
         <v>28</v>
       </c>
       <c r="B7" s="18"/>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
       <c r="G7" s="7"/>
       <c r="H7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="54" t="s">
+      <c r="I7" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="54"/>
-      <c r="K7" s="54"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
       <c r="L7" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="54" t="s">
+      <c r="M7" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="54"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="57"/>
+      <c r="P7" s="57"/>
     </row>
     <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
@@ -2248,50 +2248,50 @@
       <c r="Q8" s="9"/>
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="E9" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="52" t="s">
+      <c r="F9" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="G9" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="52" t="s">
+      <c r="H9" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52" t="s">
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49" t="s">
         <v>44</v>
       </c>
       <c r="Q9" s="8"/>
     </row>
     <row r="10" spans="1:18" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
       <c r="H10" s="37" t="s">
         <v>37</v>
       </c>
@@ -2316,7 +2316,7 @@
       <c r="O10" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="P10" s="52"/>
+      <c r="P10" s="49"/>
       <c r="Q10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -2530,35 +2530,35 @@
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="49"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="38"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
       <c r="H19" s="11"/>
       <c r="I19" s="15"/>
-      <c r="J19" s="49" t="s">
+      <c r="J19" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="K19" s="49"/>
+      <c r="K19" s="53"/>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
     </row>
     <row r="20" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="55"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="39"/>
       <c r="H20" s="11"/>
-      <c r="J20" s="55" t="s">
+      <c r="J20" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="K20" s="55"/>
+      <c r="K20" s="48"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="19"/>
@@ -2595,16 +2595,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="22">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="H9:O9"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="D9:D10"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="J19:K19"/>
@@ -2617,6 +2607,16 @@
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="I6:P6"/>
     <mergeCell ref="M7:P7"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="H9:O9"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="D9:D10"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.5" bottom="0.25" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
